--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20231.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -88,19 +88,10 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>LOYO</t>
-  </si>
-  <si>
     <t>MONTERO</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
   </si>
 </sst>
 </file>
@@ -579,19 +570,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>90</v>
+        <v>93.33</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -670,16 +661,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H2">
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -693,16 +687,19 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -716,16 +713,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -739,16 +739,19 @@
         <v>30</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>30</v>
       </c>
-      <c r="E5">
-        <v>29</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -762,16 +765,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>96.43000000000001</v>
+      </c>
+      <c r="H6">
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -827,16 +833,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>77.78</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -862,7 +868,7 @@
         <v>96</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -879,16 +885,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -902,16 +908,16 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>8.6</v>
@@ -931,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>89.29000000000001</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -950,7 +956,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -988,10 +994,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1011,10 +1017,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1023,29 +1029,6 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920164</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20231.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
   </si>
 </sst>
 </file>
@@ -833,16 +824,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>69.44</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -859,16 +850,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -885,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -920,7 +911,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -937,16 +928,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>96.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -986,52 +977,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920067</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920067</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20231.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>ARMANDO GABRIEL</t>
   </si>
 </sst>
 </file>
@@ -947,7 +956,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -977,6 +986,29 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920324</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20231.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>ARMANDO GABRIEL</t>
   </si>
 </sst>
 </file>
@@ -956,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -986,29 +977,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920324</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20231.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20231.xlsx
@@ -833,7 +833,7 @@
         <v>69.44</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -859,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -885,7 +885,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -911,7 +911,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -937,7 +937,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20231.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20231.xlsx
@@ -833,7 +833,7 @@
         <v>69.44</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -859,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -885,7 +885,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -911,7 +911,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -937,7 +937,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
